--- a/tabelas/2022.xlsx
+++ b/tabelas/2022.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\certidaodoisjs-portfolio\tabelas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\certidaodoisjs-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1346C93A-FF07-4800-A78D-6F8AF78C9EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA51608-17DC-4D16-8797-049BE0CCA113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="1041">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -26517,9 +26517,6 @@
       <c r="F1000" t="s">
         <v>1037</v>
       </c>
-      <c r="G1000" t="s">
-        <v>1039</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tabelas/2022.xlsx
+++ b/tabelas/2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\certidaodoisjs-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA51608-17DC-4D16-8797-049BE0CCA113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCEBC4AB-8CF9-4700-926E-ABF48EC83929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="1041">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -26512,10 +26512,13 @@
         <v>2022</v>
       </c>
       <c r="E1000" s="2">
-        <v>0</v>
+        <v>620.35</v>
       </c>
       <c r="F1000" t="s">
         <v>1037</v>
+      </c>
+      <c r="G1000" t="s">
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
